--- a/apps/profit-discovery-audit/Cool_Hollow_Coaching_Milestone_4_Profit_Discovery_Audit_Template.xlsx
+++ b/apps/profit-discovery-audit/Cool_Hollow_Coaching_Milestone_4_Profit_Discovery_Audit_Template.xlsx
@@ -36,17 +36,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00E8C766"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
     <font>
@@ -57,7 +57,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -75,11 +75,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <i val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -88,12 +88,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E4643"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00589BA8"/>
+        <fgColor rgb="001A1A1A"/>
       </patternFill>
     </fill>
     <fill>
@@ -103,12 +98,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B4D351"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F3"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -150,19 +145,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/apps/profit-discovery-audit/Cool_Hollow_Coaching_Milestone_4_Profit_Discovery_Audit_Template.xlsx
+++ b/apps/profit-discovery-audit/Cool_Hollow_Coaching_Milestone_4_Profit_Discovery_Audit_Template.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Customer Service Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Examples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="P&amp;L" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Customer Service Breakdown" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="10">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,12 +43,32 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005A5A5A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
@@ -62,21 +85,8 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="005A5A5A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
       <color rgb="006B6B6B"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -93,12 +103,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8C766"/>
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,11 +143,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -145,19 +156,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,10 +537,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001A1A1A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -536,125 +554,164 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 4: The Profit Discovery Audit</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>How to use this template</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>This template has two tabs. Fill in your P&amp;L on the first tab (one row per line item, one column per month). Fill in your customer and service breakdown on the second tab. Upload both tabs into the tool to run all five profit checks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Two data tabs. Fill in your P&amp;L on the first (one row per line item, one column per month) and your customer and service breakdown on the second. Then upload this same file into both upload boxes in the tool, each box automatically reads the tab it needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Three steps: fill in the data tab(s), save this file, then upload this same file into the tool. The Examples and Starter Ideas tabs are for reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads them, only type your real data on the data tab(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>On the "P&amp;L" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>What to put here</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Revenue, Cost of Goods Sold, Rent, Software, Discounts, and so on.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>One row per P&amp;L line: Revenue, Cost of Goods Sold, Rent, Software, Discounts, and so on. Straight from your accounting export is fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Month 1, Month 2, Month 3</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Rename these to your actual months (e.g. Jan 2026), add more columns if you have more months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Rename these to your actual months (e.g. Jan 2026). Add more columns if you have more months, the more months, the better the audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>On the "Customer Service Breakdown" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>What to put here</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>customer or service. One row per customer or per service line.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>The customer or service name.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Revenue from this customer or service.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Direct Cost</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>The direct cost of serving this customer or delivering this service.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Fill in the data tab, save the file, then upload it straight into the tool.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="7">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -663,10 +720,251 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="006B6B6B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 4: The Profit Discovery Audit</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Filled-in examples, for reference only. Type your own data on the data tab(s), not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, anything you type here is ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Example for the "P&amp;L" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Month 1</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Month 2</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Month 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>88000</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>91000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>51000</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>53000</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Software Subscriptions</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>420</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Discounts Given</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>3100</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Example for the "Customer Service Breakdown" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Direct Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Acme Co</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Bolt Industries</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Onboarding Package</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C8A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -681,303 +979,300 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 4: The Profit Discovery Audit</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Month 1</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Month 2</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Month 3</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Software Subscriptions</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>400</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>420</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Your data starts here, replace or delete the example rows above</t>
-        </is>
-      </c>
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="14" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C8A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -992,298 +1287,290 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 4: The Profit Discovery Audit</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Direct Cost</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>customer</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Acme Co</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>9000</v>
-      </c>
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Onboarding Package</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Your data starts here, replace or delete the example rows above</t>
-        </is>
-      </c>
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="13" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="A8:A42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: customer, service" type="list">
+    <dataValidation sqref="A5:A44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: customer, service" promptTitle="Pick from the list" prompt="One row per customer or per service line" type="list">
       <formula1>"customer,service"</formula1>
     </dataValidation>
   </dataValidations>
